--- a/agriculture 9.xlsx
+++ b/agriculture 9.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Production (Million Tonnes)</t>
   </si>
   <si>
-    <t xml:space="preserve">Yield(kg./Ha</t>
+    <t xml:space="preserve">Yield(kg./Ha)</t>
   </si>
   <si>
     <t xml:space="preserve">1951-52</t>
@@ -462,7 +462,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G1048576"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="25.9"/>

--- a/agriculture 9.xlsx
+++ b/agriculture 9.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -245,6 +245,35 @@
   </si>
   <si>
     <t xml:space="preserve">2021-22</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Unit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Area - Million Hectares,Production - Million Tonnes, Yield – kg./Ha</t>
+    </r>
   </si>
   <si>
     <r>
@@ -254,7 +283,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source</t>
     </r>
@@ -264,7 +292,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">: EPWRF (Economic&amp; Political Weekly Research Foundation) (1950-2022)</t>
     </r>
@@ -277,7 +304,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Description</t>
     </r>
@@ -287,7 +313,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">:  Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
     </r>
@@ -301,7 +326,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -337,14 +362,39 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -420,12 +470,8 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -436,11 +482,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -461,12 +511,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G1048576"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D75"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="25.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="28.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1022" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="52.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -479,1233 +530,1025 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-    </row>
-    <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="6" t="n">
         <v>-0.0511312795602792</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="6" t="n">
         <v>2.75878330582411</v>
       </c>
-      <c r="D2" s="7" t="n">
+      <c r="D2" s="6" t="n">
         <v>2.76752767527675</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="6" t="n">
         <v>5.17969049750606</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="6" t="n">
         <v>14.7544745296007</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="6" t="n">
         <v>9.15619389587075</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="6" t="n">
         <v>6.20136186770428</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="6" t="n">
         <v>18.376324735053</v>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="6" t="n">
         <v>11.5131578947368</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="6" t="n">
         <v>-1.60293107396383</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="6" t="n">
         <v>-3.56418918918919</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="6" t="n">
         <v>-2.06489675516224</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="6" t="n">
         <v>1.62904351873401</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="6" t="n">
         <v>-2.25959012086181</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="6" t="n">
         <v>-3.76506024096386</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.549576368216154</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="6" t="n">
         <v>4.48028673835126</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="6" t="n">
         <v>3.91236306729263</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="6" t="n">
         <v>-1.00204964700523</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="6" t="n">
         <v>-6.08919382504288</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="6" t="n">
         <v>-5.12048192771084</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="6" t="n">
         <v>4.03726708074534</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="6" t="n">
         <v>16.8767123287671</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="6" t="n">
         <v>12.2222222222222</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="6" t="n">
         <v>0.597014925373118</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="6" t="n">
         <v>1.37521487732459</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="6" t="n">
         <v>0.848656294200856</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="6" t="n">
         <v>1.13199252665128</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="6" t="n">
         <v>6.84445814706336</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="6" t="n">
         <v>5.61009817671809</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="6" t="n">
         <v>1.05411866985439</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="6" t="n">
         <v>2.36618092627328</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="6" t="n">
         <v>1.32802124833997</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="6" t="n">
         <v>0.634476825465114</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="6" t="n">
         <v>-3.28400281888653</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="6" t="n">
         <v>-3.93184796854522</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="6" t="n">
         <v>2.84173710288544</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="6" t="n">
         <v>3.27421555252387</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-    </row>
-    <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="6" t="n">
         <v>-0.374011540927544</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="6" t="n">
         <v>9.02649851211563</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="6" t="n">
         <v>7.79392338177014</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="6" t="n">
         <v>1.08334227180091</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="6" t="n">
         <v>-18.8978424746556</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="6" t="n">
         <v>-17.2794117647059</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-    </row>
-    <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="6" t="n">
         <v>-1.96307300509337</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="6" t="n">
         <v>5.57692307692308</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="6" t="n">
         <v>4.74074074074073</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-    </row>
-    <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B18" s="6" t="n">
         <v>0.855070895118537</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="6" t="n">
         <v>25.9107468123862</v>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="6" t="n">
         <v>18.8118811881188</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="6" t="n">
         <v>5.99914144666236</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="6" t="n">
         <v>0.771549125979498</v>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="6" t="n">
         <v>0.357142857142856</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="6" t="n">
         <v>0.404981269616278</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="6" t="n">
         <v>5.04845077162339</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="6" t="n">
         <v>2.6097271648873</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="6" t="n">
         <v>2.63184430775436</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="6" t="n">
         <v>10.0102494021182</v>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="6" t="n">
         <v>9.71098265895953</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B22" s="6" t="n">
         <v>-1.28708980153271</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="6" t="n">
         <v>-2.61904761904762</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="6" t="n">
         <v>-1.36986301369864</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="7" t="n">
+      <c r="B23" s="6" t="n">
         <v>-1.83139245545935</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="6" t="n">
         <v>-7.38811523333687</v>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="6" t="n">
         <v>-5.34188034188035</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="7" t="n">
+      <c r="B24" s="6" t="n">
         <v>4.49153401601947</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="6" t="n">
         <v>8.65472910927456</v>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="6" t="n">
         <v>3.61173814898419</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B25" s="6" t="n">
         <v>-3.89093731806714</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="6" t="n">
         <v>-5.12360025353897</v>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="D25" s="6" t="n">
         <v>-1.19825708061002</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="B26" s="6" t="n">
         <v>4.72488642099951</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="6" t="n">
         <v>20.2538692795903</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="6" t="n">
         <v>14.773980154355</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-    </row>
-    <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="7" t="n">
+      <c r="B27" s="6" t="n">
         <v>-2.27513737587969</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="6" t="n">
         <v>-7.58333333333333</v>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D27" s="6" t="n">
         <v>-5.37944284341979</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-    </row>
-    <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="7" t="n">
+      <c r="B28" s="6" t="n">
         <v>2.61418565650586</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="6" t="n">
         <v>14.6478308786695</v>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="6" t="n">
         <v>11.6751269035533</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-    </row>
-    <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="7" t="n">
+      <c r="B29" s="6" t="n">
         <v>1.27860026917901</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="6" t="n">
         <v>4.62291357161584</v>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="D29" s="6" t="n">
         <v>3.27272727272727</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-    </row>
-    <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="7" t="n">
+      <c r="B30" s="6" t="n">
         <v>-2.27812055054579</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="6" t="n">
         <v>-15.5278984296692</v>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D30" s="6" t="n">
         <v>-13.556338028169</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-    </row>
-    <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="7" t="n">
+      <c r="B31" s="6" t="n">
         <v>1.22389509470615</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="6" t="n">
         <v>17.6307722733116</v>
       </c>
-      <c r="D31" s="7" t="n">
+      <c r="D31" s="6" t="n">
         <v>16.2932790224033</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-    </row>
-    <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="7" t="n">
+      <c r="B32" s="6" t="n">
         <v>1.04596487861051</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="6" t="n">
         <v>2.37895090786819</v>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="D32" s="6" t="n">
         <v>1.31348511383538</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-    </row>
-    <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="7" t="n">
+      <c r="B33" s="6" t="n">
         <v>-2.88698955365622</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="6" t="n">
         <v>-3.39108301174152</v>
       </c>
-      <c r="D33" s="7" t="n">
+      <c r="D33" s="6" t="n">
         <v>-0.518582541054447</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-    </row>
-    <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="7" t="n">
+      <c r="B34" s="6" t="n">
         <v>5.24154116956777</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="6" t="n">
         <v>18.544960054394</v>
       </c>
-      <c r="D34" s="7" t="n">
+      <c r="D34" s="6" t="n">
         <v>12.5977410947003</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-    </row>
-    <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="7" t="n">
+      <c r="B35" s="6" t="n">
         <v>-3.41943876602863</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="6" t="n">
         <v>-4.22999713220532</v>
       </c>
-      <c r="D35" s="7" t="n">
+      <c r="D35" s="6" t="n">
         <v>-0.848765432098764</v>
       </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-    </row>
-    <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="7" t="n">
+      <c r="B36" s="6" t="n">
         <v>-0.317490860111602</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="6" t="n">
         <v>2.62015271747267</v>
       </c>
-      <c r="D36" s="7" t="n">
+      <c r="D36" s="6" t="n">
         <v>2.95719844357976</v>
       </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-    </row>
-    <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="7" t="n">
+      <c r="B37" s="6" t="n">
         <v>0.415017855419375</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="6" t="n">
         <v>-3.91742048438868</v>
       </c>
-      <c r="D37" s="7" t="n">
+      <c r="D37" s="6" t="n">
         <v>-4.31065759637188</v>
       </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-    </row>
-    <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="7" t="n">
+      <c r="B38" s="6" t="n">
         <v>-5.40176855055748</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="6" t="n">
         <v>-1.76144560018223</v>
       </c>
-      <c r="D38" s="7" t="n">
+      <c r="D38" s="6" t="n">
         <v>3.84606270290766</v>
       </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-    </row>
-    <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="s">
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="7" t="n">
+      <c r="B39" s="6" t="n">
         <v>6.20808778703517</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="6" t="n">
         <v>20.6198315171188</v>
       </c>
-      <c r="D39" s="7" t="n">
+      <c r="D39" s="6" t="n">
         <v>13.5746124473248</v>
       </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-    </row>
-    <row r="40" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="7" t="n">
+      <c r="B40" s="6" t="n">
         <v>-1.11929589591505</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="6" t="n">
         <v>1.35195745498815</v>
       </c>
-      <c r="D40" s="7" t="n">
+      <c r="D40" s="6" t="n">
         <v>2.49678525503645</v>
       </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-    </row>
-    <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="7" t="n">
+      <c r="B41" s="6" t="n">
         <v>-0.183823529411764</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="6" t="n">
         <v>2.49715513971425</v>
       </c>
-      <c r="D41" s="7" t="n">
+      <c r="D41" s="6" t="n">
         <v>2.67838473601674</v>
       </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-    </row>
-    <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="7" t="n">
+      <c r="B42" s="6" t="n">
         <v>-3.72201221285258</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="6" t="n">
         <v>-3.55887250971442</v>
       </c>
-      <c r="D42" s="7" t="n">
+      <c r="D42" s="6" t="n">
         <v>0.175640674816568</v>
       </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-    </row>
-    <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="7" t="n">
+      <c r="B43" s="6" t="n">
         <v>1.46984798147589</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="6" t="n">
         <v>6.59375799437194</v>
       </c>
-      <c r="D43" s="7" t="n">
+      <c r="D43" s="6" t="n">
         <v>5.05097989391099</v>
       </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-    </row>
-    <row r="44" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="7" t="n">
+      <c r="B44" s="6" t="n">
         <v>-0.287726957039391</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="6" t="n">
         <v>2.57394852102959</v>
       </c>
-      <c r="D44" s="7" t="n">
+      <c r="D44" s="6" t="n">
         <v>2.86213611020403</v>
       </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-    </row>
-    <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="s">
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="7" t="n">
+      <c r="B45" s="6" t="n">
         <v>0.328358208955226</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="6" t="n">
         <v>3.8020589611605</v>
       </c>
-      <c r="D45" s="7" t="n">
+      <c r="D45" s="6" t="n">
         <v>3.46504094674278</v>
       </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-    </row>
-    <row r="46" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="7" t="n">
+      <c r="B46" s="6" t="n">
         <v>-2.0827134781315</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="6" t="n">
         <v>-5.26879296742928</v>
       </c>
-      <c r="D46" s="7" t="n">
+      <c r="D46" s="6" t="n">
         <v>-3.25467490184268</v>
       </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-    </row>
-    <row r="47" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="s">
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="7" t="n">
+      <c r="B47" s="6" t="n">
         <v>2.43087207535702</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="6" t="n">
         <v>9.57111415144844</v>
       </c>
-      <c r="D47" s="7" t="n">
+      <c r="D47" s="6" t="n">
         <v>6.96854902651749</v>
       </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-    </row>
-    <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="s">
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="7" t="n">
+      <c r="B48" s="6" t="n">
         <v>0.0692178384257947</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="6" t="n">
         <v>-2.67100977198697</v>
       </c>
-      <c r="D48" s="7" t="n">
+      <c r="D48" s="6" t="n">
         <v>-2.72223137319497</v>
       </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-    </row>
-    <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="s">
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="7" t="n">
+      <c r="B49" s="6" t="n">
         <v>0.464426877470348</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="6" t="n">
         <v>5.25435073627845</v>
       </c>
-      <c r="D49" s="7" t="n">
+      <c r="D49" s="6" t="n">
         <v>4.76091030185357</v>
       </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-    </row>
-    <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="7" t="n">
+      <c r="B50" s="6" t="n">
         <v>0.31474377889249</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="6" t="n">
         <v>4.06995230524643</v>
       </c>
-      <c r="D50" s="7" t="n">
+      <c r="D50" s="6" t="n">
         <v>3.74393207152748</v>
       </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-    </row>
-    <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="s">
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="7" t="n">
+      <c r="B51" s="6" t="n">
         <v>-1.26482988528286</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="6" t="n">
         <v>-5.4180670129341</v>
       </c>
-      <c r="D51" s="7" t="n">
+      <c r="D51" s="6" t="n">
         <v>-4.21124244375661</v>
       </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-    </row>
-    <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="s">
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="7" t="n">
+      <c r="B52" s="6" t="n">
         <v>0.0695134061568847</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="6" t="n">
         <v>7.39743727791535</v>
       </c>
-      <c r="D52" s="7" t="n">
+      <c r="D52" s="6" t="n">
         <v>7.32405514863348</v>
       </c>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-    </row>
-    <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="7" t="n">
+      <c r="B53" s="6" t="n">
         <v>-7.35337898183983</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="6" t="n">
         <v>-17.9617004210948</v>
       </c>
-      <c r="D53" s="7" t="n">
+      <c r="D53" s="6" t="n">
         <v>-11.4560811493463</v>
       </c>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-    </row>
-    <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="7" t="n">
+      <c r="B54" s="6" t="n">
         <v>7.10154241645244</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="6" t="n">
         <v>21.1610143599144</v>
       </c>
-      <c r="D54" s="7" t="n">
+      <c r="D54" s="6" t="n">
         <v>13.1385570351099</v>
       </c>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-    </row>
-    <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="7" t="n">
+      <c r="B55" s="6" t="n">
         <v>-2.68026802680267</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="6" t="n">
         <v>-6.58160177526731</v>
       </c>
-      <c r="D55" s="7" t="n">
+      <c r="D55" s="6" t="n">
         <v>-4.01549113243607</v>
       </c>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-    </row>
-    <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="s">
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="7" t="n">
+      <c r="B56" s="6" t="n">
         <v>1.95252286507039</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="6" t="n">
         <v>5.39329482265292</v>
       </c>
-      <c r="D56" s="7" t="n">
+      <c r="D56" s="6" t="n">
         <v>3.37861976211491</v>
       </c>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-    </row>
-    <row r="57" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="s">
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="7" t="n">
+      <c r="B57" s="6" t="n">
         <v>1.32043140812419</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="6" t="n">
         <v>4.02622682102245</v>
       </c>
-      <c r="D57" s="7" t="n">
+      <c r="D57" s="6" t="n">
         <v>2.67615296658621</v>
       </c>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-    </row>
-    <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6" t="s">
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="7" t="n">
+      <c r="B58" s="6" t="n">
         <v>-0.0994826900119317</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="6" t="n">
         <v>6.34725231435886</v>
       </c>
-      <c r="D58" s="7" t="n">
+      <c r="D58" s="6" t="n">
         <v>6.45067090343048</v>
       </c>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
-    </row>
-    <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="s">
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="7" t="n">
+      <c r="B59" s="6" t="n">
         <v>0.318661621190985</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="6" t="n">
         <v>1.7965458165486</v>
       </c>
-      <c r="D59" s="7" t="n">
+      <c r="D59" s="6" t="n">
         <v>1.47251643620336</v>
       </c>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
-    </row>
-    <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="s">
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="7" t="n">
+      <c r="B60" s="6" t="n">
         <v>-2.67024022235457</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="6" t="n">
         <v>-7.45963156697749</v>
       </c>
-      <c r="D60" s="7" t="n">
+      <c r="D60" s="6" t="n">
         <v>-4.92437259726631</v>
       </c>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-    </row>
-    <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6" t="s">
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="7" t="n">
+      <c r="B61" s="6" t="n">
         <v>2.26415094339623</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="6" t="n">
         <v>11.2115999016958</v>
       </c>
-      <c r="D61" s="7" t="n">
+      <c r="D61" s="6" t="n">
         <v>8.74868670901325</v>
       </c>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-    </row>
-    <row r="62" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="6" t="s">
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="7" t="n">
+      <c r="B62" s="6" t="n">
         <v>0.0199461454074124</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="6" t="n">
         <v>7.04499248651993</v>
       </c>
-      <c r="D62" s="7" t="n">
+      <c r="D62" s="6" t="n">
         <v>7.02247315497215</v>
       </c>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-    </row>
-    <row r="63" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6" t="s">
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="7" t="n">
+      <c r="B63" s="6" t="n">
         <v>-2.76199022833783</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="6" t="n">
         <v>-1.41205615194054</v>
       </c>
-      <c r="D63" s="7" t="n">
+      <c r="D63" s="6" t="n">
         <v>1.39010240462458</v>
       </c>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-    </row>
-    <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="6" t="s">
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="7" t="n">
+      <c r="B64" s="6" t="n">
         <v>2.3687448728466</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="6" t="n">
         <v>2.93575676354803</v>
       </c>
-      <c r="D64" s="7" t="n">
+      <c r="D64" s="6" t="n">
         <v>0.555850520726975</v>
       </c>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-    </row>
-    <row r="65" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="6" t="s">
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="7" t="n">
+      <c r="B65" s="6" t="n">
         <v>0.921566663327655</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="6" t="n">
         <v>-4.44281703893568</v>
       </c>
-      <c r="D65" s="7" t="n">
+      <c r="D65" s="6" t="n">
         <v>-5.31251650007515</v>
       </c>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-    </row>
-    <row r="66" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="6" t="s">
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="7" t="n">
+      <c r="B66" s="6" t="n">
         <v>-2.42183622828784</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="6" t="n">
         <v>0.149018606037377</v>
       </c>
-      <c r="D66" s="7" t="n">
+      <c r="D66" s="6" t="n">
         <v>2.63371237630345</v>
       </c>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-    </row>
-    <row r="67" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="6" t="s">
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B67" s="7" t="n">
+      <c r="B67" s="6" t="n">
         <v>1.50544196928084</v>
       </c>
-      <c r="C67" s="7" t="n">
+      <c r="C67" s="6" t="n">
         <v>7.12524445200238</v>
       </c>
-      <c r="D67" s="7" t="n">
+      <c r="D67" s="6" t="n">
         <v>5.53765395722841</v>
       </c>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
-    </row>
-    <row r="68" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6" t="s">
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="7" t="n">
+      <c r="B68" s="6" t="n">
         <v>-2.08437719210343</v>
       </c>
-      <c r="C68" s="7" t="n">
+      <c r="C68" s="6" t="n">
         <v>3.02404952774031</v>
       </c>
-      <c r="D68" s="7" t="n">
+      <c r="D68" s="6" t="n">
         <v>5.21025974077405</v>
       </c>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-    </row>
-    <row r="69" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6" t="s">
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="7" t="n">
+      <c r="B69" s="6" t="n">
         <v>-2.13898270391976</v>
       </c>
-      <c r="C69" s="7" t="n">
+      <c r="C69" s="6" t="n">
         <v>1.35978428351309</v>
       </c>
-      <c r="D69" s="7" t="n">
+      <c r="D69" s="6" t="n">
         <v>3.57839188792446</v>
       </c>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
-    </row>
-    <row r="70" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="6" t="s">
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="7" t="n">
+      <c r="B70" s="6" t="n">
         <v>3.54528341351181</v>
       </c>
-      <c r="C70" s="7" t="n">
+      <c r="C70" s="6" t="n">
         <v>4.31345722646601</v>
       </c>
-      <c r="D70" s="7" t="n">
+      <c r="D70" s="6" t="n">
         <v>0.743863219288854</v>
       </c>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-    </row>
-    <row r="71" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="6" t="s">
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7" t="n">
+      <c r="B71" s="6"/>
+      <c r="C71" s="6" t="n">
         <v>3.93471291168754</v>
       </c>
-      <c r="D71" s="7"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-    </row>
-    <row r="72" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="6" t="s">
+      <c r="D71" s="6"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7" t="n">
+      <c r="B72" s="6"/>
+      <c r="C72" s="6" t="n">
         <v>0.522293886707792</v>
       </c>
-      <c r="D72" s="7"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-    </row>
-    <row r="73" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="8" t="s">
+      <c r="D72" s="6"/>
+    </row>
+    <row r="73" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="8"/>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
     </row>
     <row r="74" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="9" t="s">
+      <c r="A74" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+    </row>
+    <row r="75" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="9"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A73:D73"/>
     <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A75:D75"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
